--- a/Ultrasound/stats.xlsx
+++ b/Ultrasound/stats.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inquismedicalcom-my.sharepoint.com/personal/ronald_inquismedical_com/Documents/Documents/2026/PyTorch_3/Ultrasound/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="8_{DE95A5DA-51AF-45FC-B4D2-B9B005D8766F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{510AA4A5-7B54-4FAF-B39C-D5BBCA99A0C8}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="8_{DE95A5DA-51AF-45FC-B4D2-B9B005D8766F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{742499DA-0A5A-45BB-8388-F50DA7EFD65C}"/>
   <bookViews>
-    <workbookView xWindow="22332" yWindow="3024" windowWidth="16152" windowHeight="12972" xr2:uid="{F985D92A-DF8F-4CBF-B2C0-EC294213CAA0}"/>
+    <workbookView xWindow="23016" yWindow="852" windowWidth="16152" windowHeight="12972" activeTab="1" xr2:uid="{F985D92A-DF8F-4CBF-B2C0-EC294213CAA0}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Base_AirNeedsFix" sheetId="1" r:id="rId1"/>
+    <sheet name="AllWithRm" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="12">
   <si>
     <t xml:space="preserve">QCM STATE </t>
   </si>
@@ -72,6 +74,9 @@
   </si>
   <si>
     <t>20MHz</t>
+  </si>
+  <si>
+    <t>Rm (Ohm)</t>
   </si>
 </sst>
 </file>
@@ -507,7 +512,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="2">
-        <v>4999504</v>
+        <v>4999509</v>
       </c>
       <c r="D5" s="1">
         <v>6.67</v>
@@ -521,13 +526,13 @@
         <v>6</v>
       </c>
       <c r="C6" s="2">
-        <v>4997503</v>
+        <v>4997508</v>
       </c>
       <c r="D6" s="1">
         <v>1.54</v>
       </c>
       <c r="E6" s="1">
-        <v>726</v>
+        <v>728</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -535,13 +540,13 @@
         <v>7</v>
       </c>
       <c r="C7" s="2">
-        <v>4990030</v>
+        <v>4990025</v>
       </c>
       <c r="D7" s="1">
         <v>4</v>
       </c>
       <c r="E7" s="1">
-        <v>3694</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -582,13 +587,13 @@
         <v>5</v>
       </c>
       <c r="C13" s="2">
-        <v>9998994.5</v>
+        <v>9999019</v>
       </c>
       <c r="D13" s="1">
-        <v>6.67</v>
+        <v>4.71</v>
       </c>
       <c r="E13" s="1">
-        <v>6325</v>
+        <v>4542</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -596,13 +601,13 @@
         <v>6</v>
       </c>
       <c r="C14" s="2">
-        <v>9995012.5</v>
+        <v>9995017</v>
       </c>
       <c r="D14" s="1">
-        <v>1.54</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="E14" s="1">
-        <v>1456</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -610,13 +615,13 @@
         <v>7</v>
       </c>
       <c r="C15" s="2">
-        <v>9980065</v>
+        <v>9980050</v>
       </c>
       <c r="D15" s="1">
-        <v>4</v>
+        <v>2.83</v>
       </c>
       <c r="E15" s="1">
-        <v>3807</v>
+        <v>2710</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -657,13 +662,13 @@
         <v>5</v>
       </c>
       <c r="C21" s="2">
-        <v>19998019</v>
+        <v>19998039</v>
       </c>
       <c r="D21" s="1">
-        <v>6.66</v>
+        <v>3.33</v>
       </c>
       <c r="E21" s="2">
-        <v>12812</v>
+        <v>6406</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -671,13 +676,13 @@
         <v>6</v>
       </c>
       <c r="C22" s="2">
-        <v>19990015</v>
+        <v>19990035</v>
       </c>
       <c r="D22" s="1">
-        <v>1.54</v>
+        <v>0.77</v>
       </c>
       <c r="E22" s="1">
-        <v>2921</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -685,13 +690,286 @@
         <v>7</v>
       </c>
       <c r="C23" s="2">
-        <v>19960120</v>
+        <v>19960100</v>
       </c>
       <c r="D23" s="1">
+        <v>2</v>
+      </c>
+      <c r="E23" s="2">
+        <v>3836</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24A7C7A9-F99B-4649-B26F-9D5A85E6D86F}">
+  <dimension ref="A2:K20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="25.21875" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
+        <v>4999509</v>
+      </c>
+      <c r="D4" s="1">
+        <v>6.67</v>
+      </c>
+      <c r="E4" s="1">
+        <v>3162</v>
+      </c>
+      <c r="F4" s="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2">
+        <v>4997508</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="E5" s="1">
+        <v>728</v>
+      </c>
+      <c r="F5" s="1">
+        <v>650</v>
+      </c>
+      <c r="K5">
+        <f>F5-F6</f>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2">
+        <v>4990025</v>
+      </c>
+      <c r="D6" s="1">
         <v>4</v>
       </c>
-      <c r="E23" s="2">
-        <v>14250</v>
+      <c r="E6" s="1">
+        <v>1903</v>
+      </c>
+      <c r="F6" s="1">
+        <v>250</v>
+      </c>
+      <c r="I6">
+        <f>E6/E5</f>
+        <v>2.6140109890109891</v>
+      </c>
+      <c r="J6">
+        <f>E6-E5</f>
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="2">
+        <v>9999019</v>
+      </c>
+      <c r="D11" s="1">
+        <v>4.71</v>
+      </c>
+      <c r="E11" s="1">
+        <v>4542</v>
+      </c>
+      <c r="F11" s="1">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="2">
+        <v>9995017</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1027</v>
+      </c>
+      <c r="F12" s="1">
+        <v>919</v>
+      </c>
+      <c r="K12">
+        <f>F12-F13</f>
+        <v>566</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2">
+        <v>9980050</v>
+      </c>
+      <c r="D13" s="1">
+        <v>2.83</v>
+      </c>
+      <c r="E13" s="1">
+        <v>2710</v>
+      </c>
+      <c r="F13" s="1">
+        <v>353</v>
+      </c>
+      <c r="I13">
+        <f>E13/E12</f>
+        <v>2.6387536514118795</v>
+      </c>
+      <c r="J13">
+        <f>E13-E12</f>
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="2">
+        <v>19998039</v>
+      </c>
+      <c r="D18" s="1">
+        <v>3.33</v>
+      </c>
+      <c r="E18" s="2">
+        <v>6406</v>
+      </c>
+      <c r="F18" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="2">
+        <v>19990035</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0.77</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1460</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1300</v>
+      </c>
+      <c r="K19">
+        <f>F19-F20</f>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2">
+        <v>19960100</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2</v>
+      </c>
+      <c r="E20" s="2">
+        <v>3836</v>
+      </c>
+      <c r="F20" s="1">
+        <v>500</v>
+      </c>
+      <c r="I20">
+        <f>E20/E19</f>
+        <v>2.6273972602739728</v>
+      </c>
+      <c r="J20">
+        <f>E20-E19</f>
+        <v>2376</v>
       </c>
     </row>
   </sheetData>
